--- a/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,67</t>
+          <t>-2,92; 1,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,83</t>
+          <t>-2,46; 3,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,54</t>
+          <t>-2,46; 2,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,56</t>
+          <t>-4,02; 1,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,28</t>
+          <t>-3,33; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,06</t>
+          <t>-0,71; 4,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,24</t>
+          <t>-3,25; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,04</t>
+          <t>-5,34; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -0,98</t>
+          <t>-9,26; -0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,22</t>
+          <t>-2,41; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,63</t>
+          <t>-2,04; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,67</t>
+          <t>-0,78; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,94</t>
+          <t>-1,03; 2,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 345,52</t>
+          <t>-70,74; 281,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,72</t>
+          <t>-0,04; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,76</t>
+          <t>-1,96; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,42</t>
+          <t>-2,59; 2,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,15</t>
+          <t>-0,48; 6,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-85,15; 946,17</t>
+          <t>-95,3; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 3,41</t>
+          <t>-6,52; 3,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,34</t>
+          <t>-0,7; 1,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,54</t>
+          <t>-0,97; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,96</t>
+          <t>-0,88; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,71</t>
+          <t>-0,57; 1,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 182,81</t>
+          <t>-46,71; 194,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 137,22</t>
+          <t>-44,13; 128,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-59,94; 192,61</t>
+          <t>-66,34; 169,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 291,13</t>
+          <t>-45,49; 296,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,65</t>
+          <t>-2,86; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,77</t>
+          <t>-2,68; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,27</t>
+          <t>-2,36; 2,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,57</t>
+          <t>-3,95; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,99</t>
+          <t>-3,16; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,5</t>
+          <t>-0,65; 4,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,56</t>
+          <t>-3,34; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,35</t>
+          <t>-6,09; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -0,98</t>
+          <t>-8,87; -0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,3</t>
+          <t>-2,43; 0,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,61</t>
+          <t>-1,93; 2,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,81</t>
+          <t>-0,79; 2,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,01</t>
+          <t>-0,98; 2,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,74; 281,32</t>
+          <t>-70,18; 283,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,39</t>
+          <t>0,03; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,86</t>
+          <t>-2,12; 3,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,13</t>
+          <t>-2,53; 2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 6,37</t>
+          <t>-0,5; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,3; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,69</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 3,96</t>
+          <t>-6,45; 3,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,3</t>
+          <t>-0,86; 1,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,55</t>
+          <t>-1,03; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,89</t>
+          <t>-0,82; 0,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,67</t>
+          <t>-0,58; 1,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 194,47</t>
+          <t>-52,62; 178,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 128,2</t>
+          <t>-46,46; 122,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-66,34; 169,81</t>
+          <t>-64,45; 198,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,49; 296,0</t>
+          <t>-49,84; 281,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,08%</t>
+          <t>-15,29%</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,61</t>
+          <t>-2,92; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,0</t>
+          <t>-2,45; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,53</t>
+          <t>-2,35; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>150,88%</t>
+          <t>193,67%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,54</t>
+          <t>-3,22; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,1</t>
+          <t>-3,43; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,64</t>
+          <t>-0,8; 4,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,93</t>
+          <t>-3,34; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 1,34</t>
+          <t>-5,56; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -0,93</t>
+          <t>-8,99; -0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,97</t>
+          <t>-2,33; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,7</t>
+          <t>-2,12; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,51</t>
+          <t>-0,81; 2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,04</t>
+          <t>-0,68; 2,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 283,64</t>
+          <t>-66,21; 345,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>222,75%</t>
+          <t>208,35%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,15</t>
+          <t>-0,0; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,92</t>
+          <t>-2,3; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,01</t>
+          <t>-2,45; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,4</t>
+          <t>-0,47; 6,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,15; 946,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-46,82%</t>
+          <t>-48,01%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 3,81</t>
+          <t>-6,75; 3,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,25</t>
+          <t>-0,73; 1,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,47</t>
+          <t>-0,9; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,91</t>
+          <t>-0,74; 0,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,66</t>
+          <t>-0,39; 1,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 178,8</t>
+          <t>-49,07; 182,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 122,37</t>
+          <t>-40,46; 137,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 198,83</t>
+          <t>-59,94; 192,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 281,36</t>
+          <t>-32,54; 317,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuya percepción de los madres/padres es que su peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-44,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-15,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.6223363482672942</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2148391147131661</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.1817748170769309</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4469010636921822</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1335281679928006</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-0.1528726911547302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 1,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 3,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 3,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.917417196695109</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.451906048225357</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-2.350604608514646</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.673406140108253</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.83120730749653</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>2.995928778159814</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-50,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-41,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>193,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,22; 1,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 2,28</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 4,2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7960260222857545</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.6530077279810151</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6018515924959232</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.05866407364038</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5049761360819396</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4150240007519079</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.936720664559863</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-62,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.223096822931257</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.430637670328147</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.8029847895058237</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 4,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,56; 2,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; -0,98</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.555559965752691</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.277628790854789</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.992389592442458</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.200165491934035</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +783,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-31,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>122,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
+      <c r="C10" s="5" t="n">
+        <v>-0.05219924890737977</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.658240410718465</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.834582829057267</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.9351199743456058</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02560757815777116</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.6202019637580621</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,254 +814,144 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 1,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,12; 2,63</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 2,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 2,54</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-66,21; 345,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.344696753737797</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.563564882618697</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.985592628059832</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.240687043389613</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.043598101925153</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.977338604405724</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.105068817270173</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>419,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>48,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-21,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,0; 5,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,3; 3,76</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 2,42</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 6,33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-85,15; 946,17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.4440587887225374</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1329497347930274</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8920371308077175</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.5772775491307667</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3173685869357123</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.06295041424327742</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.225750390846299</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.9339758681344107</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-48,01%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.329596434099792</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.118480408151619</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.8121784347970029</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.6771316107822267</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.6620737563356406</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,83</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,8</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,96</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 3,25</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.216223865612207</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.631985403460716</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.671378278169048</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.536203178169296</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>3.455222145928858</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +959,275 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61,49%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.147123736274223</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8274263770837329</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3329758039800674</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.164369161763736</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>4.195682981719665</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4820769032849981</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2199367601869671</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>2.083532667513993</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 1,34</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 1,54</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 0,96</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 1,93</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-49,07; 182,81</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-40,46; 137,22</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-59,94; 192,61</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-32,54; 317,83</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.003945098631264413</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.296655614430176</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.454741034066009</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.4720105476387677</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.8514526180497372</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.721350996252095</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.757129159192142</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.421289455724009</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.332618719110668</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>9.46166971523653</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.903794978254425</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.803560544892724</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.082046020485621</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.623585829694207</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.4801222460023081</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-6.75223509868133</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6.830022795341577</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>8.802251914005103</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.96030058260548</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3.248251527563689</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.2040315442358968</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.2308140568026935</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.031006924283003</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.6306028855012226</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1700117269115938</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.1330671775325847</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.03319795265652278</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.6149335328125884</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7316298922380357</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.8968096629999774</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.7428388521887747</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.3914971630059254</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4906957401826276</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4045682876211028</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.5993684362164721</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3253781891108952</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.3359070563491</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.541835624156122</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.9595630682338407</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.930072975325579</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.828064833203028</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.372200161684327</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1.926070495706449</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>3.17828609565248</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1235,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
